--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.47273555742929</v>
+        <v>5.43931952808226</v>
       </c>
       <c r="D2" t="n">
-        <v>32.57501732141135</v>
+        <v>5.293440314729345</v>
       </c>
       <c r="E2" t="n">
-        <v>5.475994393899841</v>
+        <v>0.8898490890087242</v>
       </c>
       <c r="F2" t="n">
-        <v>4.848625076819791</v>
+        <v>0.7879015749832162</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.77025012042128</v>
+        <v>4.187665644568458</v>
       </c>
       <c r="D3" t="n">
-        <v>23.48007404034329</v>
+        <v>3.815512031555784</v>
       </c>
       <c r="E3" t="n">
-        <v>5.475994393899841</v>
+        <v>0.8898490890087242</v>
       </c>
       <c r="F3" t="n">
-        <v>4.848625076819791</v>
+        <v>0.7879015749832162</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.58051740234708</v>
+        <v>3.019334077881401</v>
       </c>
       <c r="D4" t="n">
-        <v>18.3233712234823</v>
+        <v>2.977547823815873</v>
       </c>
       <c r="E4" t="n">
-        <v>5.475994393899841</v>
+        <v>0.8898490890087242</v>
       </c>
       <c r="F4" t="n">
-        <v>4.848625076819791</v>
+        <v>0.7879015749832162</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.05799787651554</v>
+        <v>2.934424654933775</v>
       </c>
       <c r="D5" t="n">
-        <v>19.19332104069355</v>
+        <v>3.118914669112703</v>
       </c>
       <c r="E5" t="n">
-        <v>5.475994393899841</v>
+        <v>0.8898490890087242</v>
       </c>
       <c r="F5" t="n">
-        <v>4.848625076819791</v>
+        <v>0.7879015749832162</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.84601053066024</v>
+        <v>4.687476711232289</v>
       </c>
       <c r="D6" t="n">
-        <v>27.37662816756805</v>
+        <v>4.448702077229809</v>
       </c>
       <c r="E6" t="n">
-        <v>5.475994393899841</v>
+        <v>0.8898490890087242</v>
       </c>
       <c r="F6" t="n">
-        <v>4.848625076819791</v>
+        <v>0.7879015749832162</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.95362298007951</v>
+        <v>4.37996373426292</v>
       </c>
       <c r="D7" t="n">
-        <v>25.10864790786809</v>
+        <v>4.080155285028566</v>
       </c>
       <c r="E7" t="n">
-        <v>5.475994393899841</v>
+        <v>0.8898490890087242</v>
       </c>
       <c r="F7" t="n">
-        <v>4.848625076819791</v>
+        <v>0.7879015749832162</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
